--- a/ORCL.xlsx
+++ b/ORCL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5AF33A-2090-439E-AFC6-21562A37F0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F296CF0-57A8-4665-8711-2030B70B2263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{AD2507E4-7809-4EA5-A8F6-6E64402326AB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
   <si>
     <t>Oracle</t>
   </si>
@@ -225,9 +225,6 @@
     <t>CEO</t>
   </si>
   <si>
-    <t>FQ126</t>
-  </si>
-  <si>
     <t>Q126</t>
   </si>
   <si>
@@ -245,6 +242,12 @@
   <si>
     <t>OpenAi is to buy 300$ billion in computing power over 5 years</t>
   </si>
+  <si>
+    <t>FQ426</t>
+  </si>
+  <si>
+    <t>FY26</t>
+  </si>
 </sst>
 </file>
 
@@ -254,13 +257,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -467,43 +476,46 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -863,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="2">
-        <v>188.13</v>
+        <v>183.94</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -874,10 +886,10 @@
         <v>5</v>
       </c>
       <c r="H4" s="4">
-        <v>2873.13</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>62</v>
+        <v>2878</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -889,7 +901,7 @@
       </c>
       <c r="H5" s="4">
         <f>+H3*H4</f>
-        <v>540521.94689999998</v>
+        <v>529379.31999999995</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -897,11 +909,11 @@
         <v>7</v>
       </c>
       <c r="H6" s="4">
-        <f>19241+525</f>
-        <v>19766</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>62</v>
+        <f>31289+605</f>
+        <v>31894</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -915,11 +927,10 @@
         <v>8</v>
       </c>
       <c r="H7" s="4">
-        <f>8091+99984</f>
-        <v>108075</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>62</v>
+        <v>122342</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -934,7 +945,7 @@
       </c>
       <c r="H8" s="4">
         <f>+H5-H6+H7</f>
-        <v>628830.94689999998</v>
+        <v>619827.31999999995</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -975,7 +986,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>61</v>
@@ -986,7 +997,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1038,16 +1049,16 @@
         <v>18</v>
       </c>
       <c r="K2" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="M2" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="N2" s="25" t="s">
         <v>65</v>
-      </c>
-      <c r="N2" s="25" t="s">
-        <v>66</v>
       </c>
       <c r="P2" s="21" t="s">
         <v>51</v>
@@ -1066,6 +1077,9 @@
       </c>
       <c r="U2" s="21" t="s">
         <v>56</v>
+      </c>
+      <c r="V2" s="27" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.2">
@@ -1098,8 +1112,12 @@
       <c r="L3" s="4">
         <v>7977</v>
       </c>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
+      <c r="M3" s="4">
+        <v>8914</v>
+      </c>
+      <c r="N3" s="4">
+        <v>9913</v>
+      </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
@@ -1113,7 +1131,9 @@
       <c r="U3" s="4">
         <v>44029</v>
       </c>
-      <c r="V3" s="4"/>
+      <c r="V3" s="4">
+        <v>33989</v>
+      </c>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
@@ -1168,8 +1188,12 @@
       <c r="L4" s="4">
         <v>5877</v>
       </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
+      <c r="M4" s="4">
+        <v>6119</v>
+      </c>
+      <c r="N4" s="4">
+        <v>6824</v>
+      </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
@@ -1183,7 +1207,9 @@
       <c r="U4" s="4">
         <v>5201</v>
       </c>
-      <c r="V4" s="4"/>
+      <c r="V4" s="4">
+        <v>24541</v>
+      </c>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
@@ -1238,8 +1264,12 @@
       <c r="L5" s="4">
         <v>776</v>
       </c>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
+      <c r="M5" s="4">
+        <v>714</v>
+      </c>
+      <c r="N5" s="4">
+        <v>924</v>
+      </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
@@ -1253,7 +1283,9 @@
       <c r="U5" s="4">
         <v>2936</v>
       </c>
-      <c r="V5" s="4"/>
+      <c r="V5" s="4">
+        <v>3084</v>
+      </c>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
@@ -1308,8 +1340,12 @@
       <c r="L6" s="4">
         <v>1428</v>
       </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
+      <c r="M6" s="4">
+        <v>1443</v>
+      </c>
+      <c r="N6" s="4">
+        <v>1523</v>
+      </c>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
@@ -1323,7 +1359,9 @@
       <c r="U6" s="4">
         <v>5233</v>
       </c>
-      <c r="V6" s="4"/>
+      <c r="V6" s="4">
+        <v>5743</v>
+      </c>
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
@@ -1390,8 +1428,12 @@
       <c r="L7" s="18">
         <v>16058</v>
       </c>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
+      <c r="M7" s="18">
+        <v>17190</v>
+      </c>
+      <c r="N7" s="18">
+        <v>19184</v>
+      </c>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
@@ -1405,7 +1447,9 @@
       <c r="U7" s="18">
         <v>57399</v>
       </c>
-      <c r="V7" s="4"/>
+      <c r="V7" s="18">
+        <v>67357</v>
+      </c>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
@@ -1460,8 +1504,12 @@
       <c r="L8" s="4">
         <v>3990</v>
       </c>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
+      <c r="M8" s="4">
+        <v>4776</v>
+      </c>
+      <c r="N8" s="4">
+        <v>5224</v>
+      </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
@@ -1475,7 +1523,9 @@
       <c r="U8" s="4">
         <v>11569</v>
       </c>
-      <c r="V8" s="4"/>
+      <c r="V8" s="4">
+        <v>17597</v>
+      </c>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
@@ -1530,8 +1580,12 @@
       <c r="L9" s="4">
         <v>215</v>
       </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
+      <c r="M9" s="4">
+        <v>183</v>
+      </c>
+      <c r="N9" s="4">
+        <v>293</v>
+      </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
@@ -1545,7 +1599,9 @@
       <c r="U9" s="4">
         <v>782</v>
       </c>
-      <c r="V9" s="4"/>
+      <c r="V9" s="4">
+        <v>868</v>
+      </c>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
@@ -1600,8 +1656,12 @@
       <c r="L10" s="4">
         <v>1169</v>
       </c>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
+      <c r="M10" s="4">
+        <v>1133</v>
+      </c>
+      <c r="N10" s="4">
+        <v>1155</v>
+      </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
@@ -1615,7 +1675,9 @@
       <c r="U10" s="4">
         <v>4576</v>
       </c>
-      <c r="V10" s="4"/>
+      <c r="V10" s="4">
+        <v>4556</v>
+      </c>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
@@ -1665,7 +1727,7 @@
         <v>9401</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" ref="H11:L11" si="3">+H7-SUM(H8:H10)</f>
+        <f t="shared" ref="H11:N11" si="3">+H7-SUM(H8:H10)</f>
         <v>9974</v>
       </c>
       <c r="I11" s="4">
@@ -1684,8 +1746,14 @@
         <f t="shared" si="3"/>
         <v>10684</v>
       </c>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
+      <c r="M11" s="4">
+        <f t="shared" si="3"/>
+        <v>11098</v>
+      </c>
+      <c r="N11" s="4">
+        <f t="shared" si="3"/>
+        <v>12512</v>
+      </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4">
         <f t="shared" ref="P11:T11" si="4">+P7-SUM(P8:P10)</f>
@@ -1711,7 +1779,10 @@
         <f>+U7-SUM(U8:U10)</f>
         <v>40472</v>
       </c>
-      <c r="V11" s="4"/>
+      <c r="V11" s="4">
+        <f>+V7-SUM(V8:V10)</f>
+        <v>44336</v>
+      </c>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
@@ -1766,8 +1837,12 @@
       <c r="L12" s="4">
         <v>2149</v>
       </c>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
+      <c r="M12" s="4">
+        <v>2052</v>
+      </c>
+      <c r="N12" s="4">
+        <v>2068</v>
+      </c>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
@@ -1781,7 +1856,9 @@
       <c r="U12" s="23">
         <v>8651</v>
       </c>
-      <c r="V12" s="4"/>
+      <c r="V12" s="4">
+        <v>8331</v>
+      </c>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
@@ -1836,8 +1913,12 @@
       <c r="L13" s="4">
         <v>2561</v>
       </c>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
+      <c r="M13" s="4">
+        <v>2607</v>
+      </c>
+      <c r="N13" s="4">
+        <v>2613</v>
+      </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
@@ -1851,7 +1932,9 @@
       <c r="U13" s="4">
         <v>9860</v>
       </c>
-      <c r="V13" s="4"/>
+      <c r="V13" s="4">
+        <v>10272</v>
+      </c>
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
@@ -1906,8 +1989,12 @@
       <c r="L14" s="4">
         <v>409</v>
       </c>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
+      <c r="M14" s="4">
+        <v>389</v>
+      </c>
+      <c r="N14" s="4">
+        <v>444</v>
+      </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
@@ -1921,7 +2008,9 @@
       <c r="U14" s="4">
         <v>1602</v>
       </c>
-      <c r="V14" s="4"/>
+      <c r="V14" s="4">
+        <v>1618</v>
+      </c>
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
@@ -1976,8 +2065,12 @@
       <c r="L15" s="4">
         <v>407</v>
       </c>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
+      <c r="M15" s="4">
+        <v>413</v>
+      </c>
+      <c r="N15" s="4">
+        <v>431</v>
+      </c>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
@@ -1991,7 +2084,9 @@
       <c r="U15" s="4">
         <v>2307</v>
       </c>
-      <c r="V15" s="4"/>
+      <c r="V15" s="4">
+        <v>1671</v>
+      </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
@@ -2046,8 +2141,12 @@
       <c r="L16" s="4">
         <v>21</v>
       </c>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
+      <c r="M16" s="4">
+        <v>20</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
@@ -2061,7 +2160,9 @@
       <c r="U16" s="4">
         <v>75</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="4">
+        <v>0</v>
+      </c>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
@@ -2116,8 +2217,12 @@
       <c r="L17" s="4">
         <v>406</v>
       </c>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
+      <c r="M17" s="4">
+        <v>153</v>
+      </c>
+      <c r="N17" s="4">
+        <v>823</v>
+      </c>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
@@ -2131,7 +2236,9 @@
       <c r="U17" s="4">
         <v>299</v>
       </c>
-      <c r="V17" s="4"/>
+      <c r="V17" s="4">
+        <v>1838</v>
+      </c>
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
@@ -2181,7 +2288,7 @@
         <v>3991</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" ref="H18:U18" si="6">+H11-SUM(H12:H17)</f>
+        <f t="shared" ref="H18:V18" si="6">+H11-SUM(H12:H17)</f>
         <v>4220</v>
       </c>
       <c r="I18" s="4">
@@ -2200,8 +2307,14 @@
         <f t="shared" si="6"/>
         <v>4731</v>
       </c>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
+      <c r="M18" s="4">
+        <f t="shared" si="6"/>
+        <v>5464</v>
+      </c>
+      <c r="N18" s="4">
+        <f t="shared" si="6"/>
+        <v>6133</v>
+      </c>
       <c r="O18" s="4"/>
       <c r="P18" s="4">
         <f t="shared" si="6"/>
@@ -2227,7 +2340,10 @@
         <f t="shared" si="6"/>
         <v>17678</v>
       </c>
-      <c r="V18" s="4"/>
+      <c r="V18" s="4">
+        <f t="shared" si="6"/>
+        <v>20606</v>
+      </c>
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
@@ -2282,8 +2398,12 @@
       <c r="L19" s="4">
         <v>1057</v>
       </c>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
+      <c r="M19" s="4">
+        <v>1180</v>
+      </c>
+      <c r="N19" s="4">
+        <v>1438</v>
+      </c>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
@@ -2297,7 +2417,9 @@
       <c r="U19" s="4">
         <v>3578</v>
       </c>
-      <c r="V19" s="4"/>
+      <c r="V19" s="4">
+        <v>4599</v>
+      </c>
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
@@ -2352,8 +2474,12 @@
       <c r="L20" s="4">
         <v>2668</v>
       </c>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
+      <c r="M20" s="4">
+        <v>132</v>
+      </c>
+      <c r="N20" s="4">
+        <v>675</v>
+      </c>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
@@ -2367,7 +2493,9 @@
       <c r="U20" s="4">
         <v>60</v>
       </c>
-      <c r="V20" s="4"/>
+      <c r="V20" s="4">
+        <v>3547</v>
+      </c>
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
@@ -2417,7 +2545,7 @@
         <v>3169</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" ref="H21:U21" si="8">+H18-H19+H20</f>
+        <f t="shared" ref="H21:V21" si="8">+H18-H19+H20</f>
         <v>3390</v>
       </c>
       <c r="I21" s="4">
@@ -2436,8 +2564,14 @@
         <f t="shared" si="8"/>
         <v>6342</v>
       </c>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
+      <c r="M21" s="4">
+        <f t="shared" si="8"/>
+        <v>4416</v>
+      </c>
+      <c r="N21" s="4">
+        <f t="shared" si="8"/>
+        <v>5370</v>
+      </c>
       <c r="O21" s="4"/>
       <c r="P21" s="4">
         <f t="shared" si="8"/>
@@ -2463,7 +2597,10 @@
         <f t="shared" si="8"/>
         <v>14160</v>
       </c>
-      <c r="V21" s="4"/>
+      <c r="V21" s="4">
+        <f t="shared" si="8"/>
+        <v>19554</v>
+      </c>
       <c r="W21" s="4"/>
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
@@ -2518,8 +2655,14 @@
       <c r="L22" s="4">
         <v>207</v>
       </c>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
+      <c r="M22" s="4">
+        <f>695+22</f>
+        <v>717</v>
+      </c>
+      <c r="N22" s="4">
+        <f>1066+81</f>
+        <v>1147</v>
+      </c>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
@@ -2533,7 +2676,10 @@
       <c r="U22" s="4">
         <v>1717</v>
       </c>
-      <c r="V22" s="4"/>
+      <c r="V22" s="4">
+        <f>2467+103</f>
+        <v>2570</v>
+      </c>
       <c r="W22" s="4"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
@@ -2583,7 +2729,7 @@
         <v>2929</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" ref="H23:U23" si="10">+H21-H22</f>
+        <f t="shared" ref="H23:V23" si="10">+H21-H22</f>
         <v>3151</v>
       </c>
       <c r="I23" s="4">
@@ -2602,8 +2748,14 @@
         <f t="shared" si="10"/>
         <v>6135</v>
       </c>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
+      <c r="M23" s="4">
+        <f t="shared" si="10"/>
+        <v>3699</v>
+      </c>
+      <c r="N23" s="4">
+        <f t="shared" si="10"/>
+        <v>4223</v>
+      </c>
       <c r="O23" s="4"/>
       <c r="P23" s="4">
         <f t="shared" si="10"/>
@@ -2629,7 +2781,10 @@
         <f t="shared" si="10"/>
         <v>12443</v>
       </c>
-      <c r="V23" s="4"/>
+      <c r="V23" s="4">
+        <f t="shared" si="10"/>
+        <v>16984</v>
+      </c>
       <c r="W23" s="4"/>
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
@@ -2724,7 +2879,7 @@
         <v>1.0736803519061584</v>
       </c>
       <c r="H25" s="19">
-        <f t="shared" ref="H25:U25" si="12">+H23/H26</f>
+        <f t="shared" ref="H25:V25" si="12">+H23/H26</f>
         <v>1.1293906810035843</v>
       </c>
       <c r="I25" s="19">
@@ -2743,13 +2898,13 @@
         <f t="shared" si="12"/>
         <v>2.1421089385474859</v>
       </c>
-      <c r="M25" s="19" t="e">
+      <c r="M25" s="19">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N25" s="19" t="e">
+        <v>1.2870563674321502</v>
+      </c>
+      <c r="N25" s="19">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
+        <v>1.4673384294649061</v>
       </c>
       <c r="O25" s="4"/>
       <c r="P25" s="19" t="e">
@@ -2776,7 +2931,10 @@
         <f t="shared" si="12"/>
         <v>4.4614557188956612</v>
       </c>
-      <c r="V25" s="4"/>
+      <c r="V25" s="19">
+        <f t="shared" si="12"/>
+        <v>5.9384615384615387</v>
+      </c>
       <c r="W25" s="4"/>
       <c r="X25" s="4"/>
       <c r="Y25" s="4"/>
@@ -2831,8 +2989,12 @@
       <c r="L26" s="4">
         <v>2864</v>
       </c>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
+      <c r="M26" s="4">
+        <v>2874</v>
+      </c>
+      <c r="N26" s="4">
+        <v>2878</v>
+      </c>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
@@ -2846,7 +3008,9 @@
       <c r="U26" s="4">
         <v>2789</v>
       </c>
-      <c r="V26" s="4"/>
+      <c r="V26" s="4">
+        <v>2860</v>
+      </c>
       <c r="W26" s="4"/>
       <c r="X26" s="4"/>
       <c r="Y26" s="4"/>
@@ -2972,7 +3136,7 @@
         <v>0.10181208756677496</v>
       </c>
       <c r="H29" s="20">
-        <f t="shared" ref="H29:L33" si="13">+H3/D3-1</f>
+        <f t="shared" ref="H29:N33" si="13">+H3/D3-1</f>
         <v>0.12107065048241528</v>
       </c>
       <c r="I29" s="20">
@@ -2991,22 +3155,31 @@
         <f t="shared" si="13"/>
         <v>-0.26179900055524707</v>
       </c>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
+      <c r="M29" s="20">
+        <f t="shared" si="13"/>
+        <v>-0.19015172163168892</v>
+      </c>
+      <c r="N29" s="20" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O29" s="4"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
       <c r="S29" s="4"/>
       <c r="T29" s="20">
-        <f t="shared" ref="T29:U33" si="14">+T3/S3-1</f>
+        <f t="shared" ref="T29:V33" si="14">+T3/S3-1</f>
         <v>0.11544452941343075</v>
       </c>
       <c r="U29" s="20">
         <f t="shared" si="14"/>
         <v>0.11796968235025274</v>
       </c>
-      <c r="V29" s="4"/>
+      <c r="V29" s="20">
+        <f t="shared" si="14"/>
+        <v>-0.22803152467691745</v>
+      </c>
       <c r="W29" s="4"/>
       <c r="X29" s="4"/>
       <c r="Y29" s="4"/>
@@ -3063,8 +3236,14 @@
         <f t="shared" si="13"/>
         <v>3.917991631799163</v>
       </c>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
+      <c r="M30" s="20">
+        <f t="shared" si="13"/>
+        <v>4.4198405668733391</v>
+      </c>
+      <c r="N30" s="20" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O30" s="4"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
@@ -3078,7 +3257,10 @@
         <f t="shared" si="14"/>
         <v>2.3617398149970548E-2</v>
       </c>
-      <c r="V30" s="4"/>
+      <c r="V30" s="20">
+        <f t="shared" si="14"/>
+        <v>3.7185156700634492</v>
+      </c>
       <c r="W30" s="4"/>
       <c r="X30" s="4"/>
       <c r="Y30" s="4"/>
@@ -3135,8 +3317,14 @@
         <f t="shared" si="13"/>
         <v>6.5934065934065922E-2</v>
       </c>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
+      <c r="M31" s="20">
+        <f t="shared" si="13"/>
+        <v>1.5647226173541862E-2</v>
+      </c>
+      <c r="N31" s="20" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O31" s="4"/>
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
@@ -3150,7 +3338,10 @@
         <f t="shared" si="14"/>
         <v>-4.24005218525767E-2</v>
       </c>
-      <c r="V31" s="4"/>
+      <c r="V31" s="20">
+        <f t="shared" si="14"/>
+        <v>5.0408719346048958E-2</v>
+      </c>
       <c r="W31" s="4"/>
       <c r="X31" s="4"/>
       <c r="Y31" s="4"/>
@@ -3207,8 +3398,14 @@
         <f t="shared" si="13"/>
         <v>7.3684210526315796E-2</v>
       </c>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
+      <c r="M32" s="20">
+        <f t="shared" si="13"/>
+        <v>0.11773818745158793</v>
+      </c>
+      <c r="N32" s="20" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
@@ -3222,7 +3419,10 @@
         <f t="shared" si="14"/>
         <v>-3.6457374332535486E-2</v>
       </c>
-      <c r="V32" s="4"/>
+      <c r="V32" s="20">
+        <f t="shared" si="14"/>
+        <v>9.7458436843111063E-2</v>
+      </c>
       <c r="W32" s="4"/>
       <c r="X32" s="4"/>
       <c r="Y32" s="4"/>
@@ -3279,8 +3479,14 @@
         <f t="shared" si="13"/>
         <v>0.14218649975104913</v>
       </c>
-      <c r="M33" s="24"/>
-      <c r="N33" s="24"/>
+      <c r="M33" s="24">
+        <f t="shared" si="13"/>
+        <v>0.21656050955414008</v>
+      </c>
+      <c r="N33" s="24" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O33" s="18"/>
       <c r="P33" s="18"/>
       <c r="Q33" s="18"/>
@@ -3294,7 +3500,10 @@
         <f t="shared" si="14"/>
         <v>8.3797511376295875E-2</v>
       </c>
-      <c r="V33" s="4"/>
+      <c r="V33" s="24">
+        <f t="shared" si="14"/>
+        <v>0.1734873429850694</v>
+      </c>
       <c r="W33" s="4"/>
       <c r="X33" s="4"/>
       <c r="Y33" s="4"/>
@@ -3363,34 +3572,43 @@
         <f t="shared" si="18"/>
         <v>0.66533814920911694</v>
       </c>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
+      <c r="M34" s="20">
+        <f t="shared" ref="M34:N34" si="19">+M11/M7</f>
+        <v>0.64560791157649799</v>
+      </c>
+      <c r="N34" s="20">
+        <f t="shared" si="19"/>
+        <v>0.65221017514595492</v>
+      </c>
       <c r="O34" s="4"/>
       <c r="P34" s="20" t="e">
-        <f t="shared" ref="P34:U34" si="19">+P11/P7</f>
+        <f t="shared" ref="P34:U34" si="20">+P11/P7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q34" s="20" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R34" s="20" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S34" s="20">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.72847019257717105</v>
       </c>
       <c r="T34" s="20">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.71407261947470779</v>
       </c>
       <c r="U34" s="20">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.70509939197547</v>
       </c>
-      <c r="V34" s="4"/>
+      <c r="V34" s="20">
+        <f t="shared" ref="V34" si="21">+V11/V7</f>
+        <v>0.65822408955268197</v>
+      </c>
       <c r="W34" s="4"/>
       <c r="X34" s="4"/>
       <c r="Y34" s="4"/>
@@ -3420,19 +3638,19 @@
         <v>47</v>
       </c>
       <c r="C35" s="20">
-        <f t="shared" ref="C35:F35" si="20">+C18/C7</f>
+        <f t="shared" ref="C35:F35" si="22">+C18/C7</f>
         <v>0.26467517867180601</v>
       </c>
       <c r="D35" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.27988563480411094</v>
       </c>
       <c r="E35" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.28237951807228917</v>
       </c>
       <c r="F35" s="20" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G35" s="20">
@@ -3440,53 +3658,62 @@
         <v>0.2999173367400616</v>
       </c>
       <c r="H35" s="20">
-        <f t="shared" ref="H35:J35" si="21">+H18/H7</f>
+        <f t="shared" ref="H35:J35" si="23">+H18/H7</f>
         <v>0.30016359627285011</v>
       </c>
       <c r="I35" s="20">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.30842179759377214</v>
       </c>
       <c r="J35" s="20" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K35" s="20">
-        <f t="shared" ref="K35:L35" si="22">+K18/K7</f>
+        <f t="shared" ref="K35:L35" si="24">+K18/K7</f>
         <v>0.28654696502746885</v>
       </c>
       <c r="L35" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.29461950429692363</v>
       </c>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
+      <c r="M35" s="20">
+        <f t="shared" ref="M35:N35" si="25">+M18/M7</f>
+        <v>0.31785922047702153</v>
+      </c>
+      <c r="N35" s="20">
+        <f t="shared" si="25"/>
+        <v>0.31969349457881568</v>
+      </c>
       <c r="O35" s="4"/>
       <c r="P35" s="20" t="e">
-        <f t="shared" ref="P35:U35" si="23">+P18/P7</f>
+        <f t="shared" ref="P35:U35" si="26">+P18/P7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q35" s="20" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R35" s="20" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S35" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.26210113304239901</v>
       </c>
       <c r="T35" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.28989256245161532</v>
       </c>
       <c r="U35" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.30798445965957594</v>
       </c>
-      <c r="V35" s="4"/>
+      <c r="V35" s="20">
+        <f t="shared" ref="V35" si="27">+V18/V7</f>
+        <v>0.30592217586887777</v>
+      </c>
       <c r="W35" s="4"/>
       <c r="X35" s="4"/>
       <c r="Y35" s="4"/>
@@ -3516,19 +3743,19 @@
         <v>48</v>
       </c>
       <c r="C36" s="20">
-        <f t="shared" ref="C36:F36" si="24">+C22/C21</f>
+        <f t="shared" ref="C36:F36" si="28">+C22/C21</f>
         <v>-1.8947368421052633E-2</v>
       </c>
       <c r="D36" s="20">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>7.9779411764705876E-2</v>
       </c>
       <c r="E36" s="20">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0.16195462478184991</v>
       </c>
       <c r="F36" s="20" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G36" s="20">
@@ -3536,53 +3763,62 @@
         <v>7.5733669927421893E-2</v>
       </c>
       <c r="H36" s="20">
-        <f t="shared" ref="H36:J36" si="25">+H22/H21</f>
+        <f t="shared" ref="H36:J36" si="29">+H22/H21</f>
         <v>7.0501474926253693E-2</v>
       </c>
       <c r="I36" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0.14849187935034802</v>
       </c>
       <c r="J36" s="20" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K36" s="20">
-        <f t="shared" ref="K36:L36" si="26">+K22/K21</f>
+        <f t="shared" ref="K36:L36" si="30">+K22/K21</f>
         <v>0.14590020426028597</v>
       </c>
       <c r="L36" s="20">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>3.2639545884578999E-2</v>
       </c>
-      <c r="M36" s="20"/>
-      <c r="N36" s="20"/>
+      <c r="M36" s="20">
+        <f t="shared" ref="M36:N36" si="31">+M22/M21</f>
+        <v>0.16236413043478262</v>
+      </c>
+      <c r="N36" s="20">
+        <f t="shared" si="31"/>
+        <v>0.21359404096834264</v>
+      </c>
       <c r="O36" s="4"/>
       <c r="P36" s="20" t="e">
-        <f t="shared" ref="P36:U36" si="27">+P22/P21</f>
+        <f t="shared" ref="P36:U36" si="32">+P22/P21</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q36" s="20" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R36" s="20" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S36" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>6.826649134341442E-2</v>
       </c>
       <c r="T36" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.10850864491951281</v>
       </c>
       <c r="U36" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0.12125706214689265</v>
       </c>
-      <c r="V36" s="4"/>
+      <c r="V36" s="20">
+        <f t="shared" ref="V36" si="33">+V22/V21</f>
+        <v>0.13143090927687429</v>
+      </c>
       <c r="W36" s="4"/>
       <c r="X36" s="4"/>
       <c r="Y36" s="4"/>
